--- a/tuning/compare_pv_ft.xlsx
+++ b/tuning/compare_pv_ft.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="324" windowWidth="21768" windowHeight="10596" tabRatio="850" activeTab="9"/>
+    <workbookView xWindow="768" yWindow="324" windowWidth="21768" windowHeight="10596" tabRatio="850" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="synth_new2_test" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,10 @@
     <sheet name="Smsc" sheetId="10" r:id="rId10"/>
     <sheet name="synth_new2_val" sheetId="12" r:id="rId11"/>
     <sheet name="synth_new2_train" sheetId="13" r:id="rId12"/>
+    <sheet name="ft21SGD" sheetId="14" r:id="rId13"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">ft21SGD!$A$1:$O$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">pilot_test!$A$1:$E$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">rzeszow_test!$A$1:$E$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">rzeszow_train!$A$1:$E$56</definedName>
@@ -31,6 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">synth_old_test!$A$1:$E$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">synth_old_train!$A$1:$E$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">synth_old_val!$A$1:$E$57</definedName>
+    <definedName name="evaluation_resultsft21SGD2.pt" localSheetId="12">ft21SGD!$A$1:$O$41</definedName>
     <definedName name="merged_feval_pilot_test" localSheetId="4">pilot_test!$A$1:$E$57</definedName>
     <definedName name="merged_feval_rzeszow_test" localSheetId="5">rzeszow_test!$A$1:$E$56</definedName>
     <definedName name="merged_feval_rzeszow_train" localSheetId="6">rzeszow_train!$A$1:$E$56</definedName>
@@ -44,15 +47,39 @@
   </definedNames>
   <calcPr calcId="125725"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId13"/>
-    <pivotCache cacheId="4" r:id="rId14"/>
+    <pivotCache cacheId="5" r:id="rId14"/>
+    <pivotCache cacheId="6" r:id="rId15"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="merged_feval_pilot_test" type="6" refreshedVersion="3" background="1" saveData="1">
+  <connection id="1" name="evaluation_resultsft21SGD2.pt" type="6" refreshedVersion="3" background="1" saveData="1">
+    <textPr codePage="852" sourceFile="C:\Users\admin\Documents\GitHub\modelling\tuning\evaluation_resultsft21SGD2.pt.csv" thousands=" " comma="1">
+      <textFields count="18">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="2" name="merged_feval_pilot_test" type="6" refreshedVersion="3" background="1" saveData="1">
     <textPr codePage="852" sourceFile="C:\Users\admin\Documents\GitHub\modelling\tuning\results\merged_feval_pilot_test.csv" thousands=" " comma="1">
       <textFields count="5">
         <textField/>
@@ -63,7 +90,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="2" name="merged_feval_rzeszow_test" type="6" refreshedVersion="3" background="1" saveData="1">
+  <connection id="3" name="merged_feval_rzeszow_test" type="6" refreshedVersion="3" background="1" saveData="1">
     <textPr codePage="852" sourceFile="C:\Users\admin\Documents\GitHub\modelling\tuning\results\merged_feval_rzeszow_test.csv" thousands=" " comma="1">
       <textFields count="5">
         <textField/>
@@ -74,7 +101,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="3" name="merged_feval_rzeszow_train" type="6" refreshedVersion="3" background="1" saveData="1">
+  <connection id="4" name="merged_feval_rzeszow_train" type="6" refreshedVersion="3" background="1" saveData="1">
     <textPr codePage="852" sourceFile="C:\Users\admin\Documents\GitHub\modelling\tuning\results\merged_feval_rzeszow_train.csv" thousands=" " comma="1">
       <textFields count="5">
         <textField/>
@@ -85,7 +112,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="4" name="merged_feval_rzeszow_val" type="6" refreshedVersion="3" background="1" saveData="1">
+  <connection id="5" name="merged_feval_rzeszow_val" type="6" refreshedVersion="3" background="1" saveData="1">
     <textPr codePage="852" sourceFile="C:\Users\admin\Documents\GitHub\modelling\tuning\results\merged_feval_rzeszow_val.csv" thousands=" " comma="1">
       <textFields count="5">
         <textField/>
@@ -96,7 +123,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="5" name="merged_feval_synth_new2_test" type="6" refreshedVersion="3" background="1" saveData="1">
+  <connection id="6" name="merged_feval_synth_new2_test" type="6" refreshedVersion="3" background="1" saveData="1">
     <textPr codePage="852" sourceFile="C:\Users\admin\Documents\GitHub\modelling\tuning\results\merged_feval_synth_new2_test.csv" thousands=" " comma="1">
       <textFields count="5">
         <textField/>
@@ -107,7 +134,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="6" name="merged_feval_synth_new2_train" type="6" refreshedVersion="3" background="1" saveData="1">
+  <connection id="7" name="merged_feval_synth_new2_train" type="6" refreshedVersion="3" background="1" saveData="1">
     <textPr codePage="852" sourceFile="C:\Users\admin\Documents\GitHub\modelling\tuning\results\merged_feval_synth_new2_train.csv" thousands=" " comma="1">
       <textFields count="5">
         <textField/>
@@ -118,7 +145,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="7" name="merged_feval_synth_new2_val" type="6" refreshedVersion="3" background="1" saveData="1">
+  <connection id="8" name="merged_feval_synth_new2_val" type="6" refreshedVersion="3" background="1" saveData="1">
     <textPr codePage="852" sourceFile="C:\Users\admin\Documents\GitHub\modelling\tuning\results\merged_feval_synth_new2_val.csv" thousands=" " comma="1">
       <textFields count="5">
         <textField/>
@@ -129,7 +156,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="8" name="merged_feval_synth_old_test" type="6" refreshedVersion="3" background="1" saveData="1">
+  <connection id="9" name="merged_feval_synth_old_test" type="6" refreshedVersion="3" background="1" saveData="1">
     <textPr codePage="852" sourceFile="C:\Users\admin\Documents\GitHub\modelling\tuning\results\merged_feval_synth_old_test.csv" thousands=" " comma="1">
       <textFields count="5">
         <textField/>
@@ -140,7 +167,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="9" name="merged_feval_synth_old_train" type="6" refreshedVersion="3" background="1" saveData="1">
+  <connection id="10" name="merged_feval_synth_old_train" type="6" refreshedVersion="3" background="1" saveData="1">
     <textPr codePage="852" sourceFile="C:\Users\admin\Documents\GitHub\modelling\tuning\results\merged_feval_synth_old_train.csv" thousands=" " comma="1">
       <textFields count="5">
         <textField/>
@@ -151,7 +178,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="10" name="merged_feval_synth_old_val" type="6" refreshedVersion="3" background="1" saveData="1">
+  <connection id="11" name="merged_feval_synth_old_val" type="6" refreshedVersion="3" background="1" saveData="1">
     <textPr codePage="852" sourceFile="C:\Users\admin\Documents\GitHub\modelling\tuning\results\merged_feval_synth_old_val.csv" thousands=" " comma="1">
       <textFields count="5">
         <textField/>
@@ -166,7 +193,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="91">
   <si>
     <t>setting</t>
   </si>
@@ -365,12 +392,91 @@
   <si>
     <t>Suma z msc</t>
   </si>
+  <si>
+    <t>dataset</t>
+  </si>
+  <si>
+    <t>split</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Images</t>
+  </si>
+  <si>
+    <t>Instances</t>
+  </si>
+  <si>
+    <t>Box-P</t>
+  </si>
+  <si>
+    <t>Box-R</t>
+  </si>
+  <si>
+    <t>Mask-P</t>
+  </si>
+  <si>
+    <t>Mask-R</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>pilot</t>
+  </si>
+  <si>
+    <t>val</t>
+  </si>
+  <si>
+    <t>finloop</t>
+  </si>
+  <si>
+    <t>solar-panel</t>
+  </si>
+  <si>
+    <t>ft21SGD</t>
+  </si>
+  <si>
+    <t>pv</t>
+  </si>
+  <si>
+    <t>ariel</t>
+  </si>
+  <si>
+    <t>pools</t>
+  </si>
+  <si>
+    <t>solarpanel</t>
+  </si>
+  <si>
+    <t>rzeszow</t>
+  </si>
+  <si>
+    <t>train</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>synth_old</t>
+  </si>
+  <si>
+    <t>synth_new</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _z_ł_-;\-* #,##0.00\ _z_ł_-;_-* &quot;-&quot;??\ _z_ł_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0\ _z_ł_-;\-* #,##0\ _z_ł_-;_-* &quot;-&quot;??\ _z_ł_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,6 +489,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Czcionka tekstu podstawowego"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Czcionka tekstu podstawowego"/>
+      <family val="2"/>
       <charset val="238"/>
     </font>
   </fonts>
@@ -403,10 +516,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -414,8 +528,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Dziesiętny" xfId="1" builtinId="3"/>
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2398,7 +2515,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela przestawna1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Wartości" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela przestawna1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Wartości" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H1:I31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
@@ -2555,7 +2672,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela przestawna2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Wartości" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela przestawna2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Wartości" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E1:F58" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
@@ -2817,43 +2934,47 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_synth_new2_test" connectionId="5" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_synth_new2_test" connectionId="6" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_synth_new2_train" connectionId="6" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_synth_new2_train" connectionId="7" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="evaluation_resultsft21SGD2.pt" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_synth_old_test" connectionId="8" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_synth_old_test" connectionId="9" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_synth_old_train" connectionId="9" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_synth_old_train" connectionId="10" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_synth_old_val" connectionId="10" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_synth_old_val" connectionId="11" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_pilot_test" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_pilot_test" connectionId="2" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_rzeszow_test" connectionId="2" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_rzeszow_test" connectionId="3" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_rzeszow_train" connectionId="3" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_rzeszow_train" connectionId="4" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_rzeszow_val" connectionId="4" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_rzeszow_val" connectionId="5" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_synth_new2_val" connectionId="7" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="merged_feval_synth_new2_val" connectionId="8" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10563,6 +10684,1957 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O41"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="7.296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="7.296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" style="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="6">
+        <v>54</v>
+      </c>
+      <c r="F2" s="6">
+        <v>227</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0.379</v>
+      </c>
+      <c r="K2" s="5">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0.159</v>
+      </c>
+      <c r="N2" s="5">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="O2" s="5">
+        <v>13.514599800109799</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="6">
+        <v>54</v>
+      </c>
+      <c r="F3" s="6">
+        <v>227</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0.185</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0.121</v>
+      </c>
+      <c r="K3" s="5">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0.216</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5.5479817390441797</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="5">
+        <v>54</v>
+      </c>
+      <c r="F4" s="5">
+        <v>227</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5">
+        <v>3.6959569454193102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="5">
+        <v>54</v>
+      </c>
+      <c r="F5" s="5">
+        <v>227</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5">
+        <v>4.9389865398406902</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="6">
+        <v>8440</v>
+      </c>
+      <c r="F6" s="6">
+        <v>66301</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0.94599999999999995</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0.871</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="O6" s="5">
+        <v>296.13214635848999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="6">
+        <v>8440</v>
+      </c>
+      <c r="F7" s="6">
+        <v>66301</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0.621</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="O7" s="5">
+        <v>69.746719837188706</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="5">
+        <v>8440</v>
+      </c>
+      <c r="F8" s="5">
+        <v>66301</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.91600000000000004</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.84299999999999997</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0.878</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5">
+        <v>36.588186502456601</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="5">
+        <v>8440</v>
+      </c>
+      <c r="F9" s="5">
+        <v>66301</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.628</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5">
+        <v>94.233100891113196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="6">
+        <v>661</v>
+      </c>
+      <c r="F10" s="6">
+        <v>2767</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0.88</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0.73</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="O10" s="5">
+        <v>33.508022546768103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="6">
+        <v>661</v>
+      </c>
+      <c r="F11" s="6">
+        <v>2767</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0.66400000000000003</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="O11" s="5">
+        <v>11.8784484863281</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="5">
+        <v>661</v>
+      </c>
+      <c r="F12" s="5">
+        <v>2767</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.83399999999999996</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0.501</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5">
+        <v>7.8351464271545401</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="5">
+        <v>661</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2767</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0.43</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5">
+        <v>11.028480529785099</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="6">
+        <v>435</v>
+      </c>
+      <c r="F14" s="6">
+        <v>1692</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0.83899999999999997</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="O14" s="5">
+        <v>28.407696247100802</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="6">
+        <v>435</v>
+      </c>
+      <c r="F15" s="6">
+        <v>1692</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0.87</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0.91700000000000004</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="O15" s="5">
+        <v>10.006232261657701</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="5">
+        <v>435</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1692</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0.82599999999999996</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0.86</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5">
+        <v>7.5838963985443097</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="5">
+        <v>435</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1692</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0.54</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5">
+        <v>8.7841589450836093</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="6">
+        <v>150</v>
+      </c>
+      <c r="F18" s="6">
+        <v>374</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0.115</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0.254</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0.184</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0.214</v>
+      </c>
+      <c r="O18" s="5">
+        <v>15.5847079753875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="6">
+        <v>150</v>
+      </c>
+      <c r="F19" s="6">
+        <v>374</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="H19" s="5">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0.251</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="O19" s="5">
+        <v>7.1303606033325098</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="5">
+        <v>150</v>
+      </c>
+      <c r="F20" s="5">
+        <v>374</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="H20" s="5">
+        <v>0.38</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="J20" s="5">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5">
+        <v>5.8014714717864901</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="5">
+        <v>150</v>
+      </c>
+      <c r="F21" s="5">
+        <v>374</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0.372</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0.188</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5">
+        <v>5.8801107406616202</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="6">
+        <v>12</v>
+      </c>
+      <c r="F22" s="6">
+        <v>35</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0.501</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="O22" s="5">
+        <v>4.7051544189453098</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="6">
+        <v>12</v>
+      </c>
+      <c r="F23" s="6">
+        <v>35</v>
+      </c>
+      <c r="G23" s="5">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="H23" s="5">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="K23" s="5">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="N23" s="5">
+        <v>0.622</v>
+      </c>
+      <c r="O23" s="5">
+        <v>4.2452187538146902</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="5">
+        <v>12</v>
+      </c>
+      <c r="F24" s="5">
+        <v>35</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="H24" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="I24" s="5">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="J24" s="5">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="L24" s="5">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5">
+        <v>2.9695990085601802</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="5">
+        <v>12</v>
+      </c>
+      <c r="F25" s="5">
+        <v>35</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="H25" s="5">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="I25" s="5">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="J25" s="5">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="K25" s="5">
+        <v>0.34</v>
+      </c>
+      <c r="L25" s="5">
+        <v>0</v>
+      </c>
+      <c r="M25" s="5">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5">
+        <v>0</v>
+      </c>
+      <c r="O25" s="5">
+        <v>3.28194904327392</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="6">
+        <v>18</v>
+      </c>
+      <c r="F26" s="6">
+        <v>32</v>
+      </c>
+      <c r="G26" s="5">
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="H26" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="I26" s="5">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="J26" s="5">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="K26" s="5">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L26" s="5">
+        <v>0.222</v>
+      </c>
+      <c r="M26" s="5">
+        <v>0.219</v>
+      </c>
+      <c r="N26" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="O26" s="5">
+        <v>5.61700010299682</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="6">
+        <v>18</v>
+      </c>
+      <c r="F27" s="6">
+        <v>32</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0.441</v>
+      </c>
+      <c r="H27" s="5">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="I27" s="5">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="J27" s="5">
+        <v>0.379</v>
+      </c>
+      <c r="K27" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="L27" s="5">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="M27" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="N27" s="5">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="O27" s="5">
+        <v>4.3275735378265301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="5">
+        <v>18</v>
+      </c>
+      <c r="F28" s="5">
+        <v>32</v>
+      </c>
+      <c r="G28" s="5">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="H28" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="I28" s="5">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="J28" s="5">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="K28" s="5">
+        <v>0.108</v>
+      </c>
+      <c r="L28" s="5">
+        <v>0</v>
+      </c>
+      <c r="M28" s="5">
+        <v>0</v>
+      </c>
+      <c r="N28" s="5">
+        <v>0</v>
+      </c>
+      <c r="O28" s="5">
+        <v>3.2045903205871502</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="5">
+        <v>18</v>
+      </c>
+      <c r="F29" s="5">
+        <v>32</v>
+      </c>
+      <c r="G29" s="5">
+        <v>0.435</v>
+      </c>
+      <c r="H29" s="5">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="I29" s="5">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="J29" s="5">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0.159</v>
+      </c>
+      <c r="L29" s="5">
+        <v>0</v>
+      </c>
+      <c r="M29" s="5">
+        <v>0</v>
+      </c>
+      <c r="N29" s="5">
+        <v>0</v>
+      </c>
+      <c r="O29" s="5">
+        <v>5.4864294528961102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="6">
+        <v>789</v>
+      </c>
+      <c r="F30" s="6">
+        <v>789</v>
+      </c>
+      <c r="G30" s="5">
+        <v>6.2E-2</v>
+      </c>
+      <c r="H30" s="5">
+        <v>2.7E-2</v>
+      </c>
+      <c r="I30" s="5">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="J30" s="5">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="K30" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="L30" s="5">
+        <v>0</v>
+      </c>
+      <c r="M30" s="5">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5">
+        <v>49.576002597808802</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" s="6">
+        <v>789</v>
+      </c>
+      <c r="F31" s="6">
+        <v>789</v>
+      </c>
+      <c r="G31" s="5">
+        <v>0.999</v>
+      </c>
+      <c r="H31" s="5">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="I31" s="5">
+        <v>0.995</v>
+      </c>
+      <c r="J31" s="5">
+        <v>0.995</v>
+      </c>
+      <c r="K31" s="5">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="L31" s="5">
+        <v>0.999</v>
+      </c>
+      <c r="M31" s="5">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="N31" s="5">
+        <v>0.995</v>
+      </c>
+      <c r="O31" s="5">
+        <v>12.440945625305099</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="5">
+        <v>789</v>
+      </c>
+      <c r="F32" s="5">
+        <v>789</v>
+      </c>
+      <c r="G32" s="5">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="H32" s="5">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I32" s="5">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="J32" s="5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K32" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="L32" s="5">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5">
+        <v>8.3655719757080007</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="5">
+        <v>789</v>
+      </c>
+      <c r="F33" s="5">
+        <v>789</v>
+      </c>
+      <c r="G33" s="5">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="H33" s="5">
+        <v>6.3E-2</v>
+      </c>
+      <c r="I33" s="5">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="J33" s="5">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K33" s="5">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0</v>
+      </c>
+      <c r="M33" s="5">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5">
+        <v>11.608843564987099</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="6">
+        <v>225</v>
+      </c>
+      <c r="F34" s="6">
+        <v>225</v>
+      </c>
+      <c r="G34" s="5">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="H34" s="5">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="I34" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="J34" s="5">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="K34" s="5">
+        <v>2E-3</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5">
+        <v>22.072350978851301</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" s="6">
+        <v>225</v>
+      </c>
+      <c r="F35" s="6">
+        <v>225</v>
+      </c>
+      <c r="G35" s="5">
+        <v>1</v>
+      </c>
+      <c r="H35" s="5">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5">
+        <v>1</v>
+      </c>
+      <c r="J35" s="5">
+        <v>0.995</v>
+      </c>
+      <c r="K35" s="5">
+        <v>0.91900000000000004</v>
+      </c>
+      <c r="L35" s="5">
+        <v>1</v>
+      </c>
+      <c r="M35" s="5">
+        <v>1</v>
+      </c>
+      <c r="N35" s="5">
+        <v>1</v>
+      </c>
+      <c r="O35" s="5">
+        <v>7.9893395900726301</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="5">
+        <v>225</v>
+      </c>
+      <c r="F36" s="5">
+        <v>225</v>
+      </c>
+      <c r="G36" s="5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="H36" s="5">
+        <v>3.1E-2</v>
+      </c>
+      <c r="I36" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="J36" s="5">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="K36" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5">
+        <v>6.0775430202484104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="5">
+        <v>225</v>
+      </c>
+      <c r="F37" s="5">
+        <v>225</v>
+      </c>
+      <c r="G37" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H37" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="I37" s="5">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="J37" s="5">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="K37" s="5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0</v>
+      </c>
+      <c r="M37" s="5">
+        <v>0</v>
+      </c>
+      <c r="N37" s="5">
+        <v>0</v>
+      </c>
+      <c r="O37" s="5">
+        <v>6.2857708930969203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" s="6">
+        <v>114</v>
+      </c>
+      <c r="F38" s="6">
+        <v>114</v>
+      </c>
+      <c r="G38" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="H38" s="5">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="I38" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="J38" s="5">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="K38" s="5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0</v>
+      </c>
+      <c r="M38" s="5">
+        <v>0</v>
+      </c>
+      <c r="N38" s="5">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5">
+        <v>15.5205540657043</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="6">
+        <v>114</v>
+      </c>
+      <c r="F39" s="6">
+        <v>114</v>
+      </c>
+      <c r="G39" s="5">
+        <v>0.999</v>
+      </c>
+      <c r="H39" s="5">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="I39" s="5">
+        <v>0.995</v>
+      </c>
+      <c r="J39" s="5">
+        <v>0.995</v>
+      </c>
+      <c r="K39" s="5">
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0.999</v>
+      </c>
+      <c r="M39" s="5">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="N39" s="5">
+        <v>0.995</v>
+      </c>
+      <c r="O39" s="5">
+        <v>6.28344249725341</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="5">
+        <v>114</v>
+      </c>
+      <c r="F40" s="5">
+        <v>114</v>
+      </c>
+      <c r="G40" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="H40" s="5">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="I40" s="5">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="J40" s="5">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="K40" s="5">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L40" s="5">
+        <v>0</v>
+      </c>
+      <c r="M40" s="5">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5">
+        <v>4.3489937782287598</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" s="5">
+        <v>114</v>
+      </c>
+      <c r="F41" s="5">
+        <v>114</v>
+      </c>
+      <c r="G41" s="5">
+        <v>0.111</v>
+      </c>
+      <c r="H41" s="5">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="I41" s="5">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="J41" s="5">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="K41" s="5">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L41" s="5">
+        <v>0</v>
+      </c>
+      <c r="M41" s="5">
+        <v>0</v>
+      </c>
+      <c r="N41" s="5">
+        <v>0</v>
+      </c>
+      <c r="O41" s="5">
+        <v>4.6188910007476798</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O41"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F57"/>
